--- a/data2.xlsx
+++ b/data2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\rejoice\data_projects\crucial_sales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48935F5C-454D-4C9F-A012-D70F7C2736F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A77EDDC-4A5E-49BF-8A67-220491EE6E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="76">
   <si>
     <t>txn_id</t>
   </si>
@@ -79,9 +79,6 @@
     <t>jogger</t>
   </si>
   <si>
-    <t>basic top</t>
-  </si>
-  <si>
     <t>bum short</t>
   </si>
   <si>
@@ -241,9 +238,6 @@
     <t>07015515307</t>
   </si>
   <si>
-    <t>0946978742</t>
-  </si>
-  <si>
     <t>08167491188</t>
   </si>
   <si>
@@ -260,6 +254,12 @@
   </si>
   <si>
     <t>loan</t>
+  </si>
+  <si>
+    <t>09016978742</t>
+  </si>
+  <si>
+    <t>salaries</t>
   </si>
 </sst>
 </file>
@@ -319,17 +319,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="9">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     </dxf>
@@ -436,11 +443,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5687A707-2FB8-42A8-86F4-54A8763C6A1B}" name="Table1" displayName="Table1" ref="A1:H41" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="2" tableBorderDxfId="1">
-  <autoFilter ref="A1:H41" xr:uid="{5687A707-2FB8-42A8-86F4-54A8763C6A1B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5687A707-2FB8-42A8-86F4-54A8763C6A1B}" name="Table1" displayName="Table1" ref="A1:H43" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6">
+  <autoFilter ref="A1:H43" xr:uid="{5687A707-2FB8-42A8-86F4-54A8763C6A1B}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{C0FD0D9F-9597-4679-9F73-63FF804A0881}" name="txn_id"/>
-    <tableColumn id="2" xr3:uid="{FF9D134A-CB66-4B80-9E10-D3C9D3780E4A}" name="date" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{FF9D134A-CB66-4B80-9E10-D3C9D3780E4A}" name="date" dataDxfId="5"/>
     <tableColumn id="3" xr3:uid="{B78FB8F2-ACCF-4D34-91A8-01D998CEA763}" name="category"/>
     <tableColumn id="4" xr3:uid="{70517F54-68D9-4A92-90B1-9BD2DF311283}" name="amount"/>
     <tableColumn id="5" xr3:uid="{27CFA9CD-28BA-4548-B7C9-F1BC6E21921A}" name="type"/>
@@ -453,14 +460,14 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{95725E76-239B-411F-9E09-B19577DC4C41}" name="Table2" displayName="Table2" ref="A1:F23" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{95725E76-239B-411F-9E09-B19577DC4C41}" name="Table2" displayName="Table2" ref="A1:F23" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3" tableBorderDxfId="2">
   <autoFilter ref="A1:F23" xr:uid="{95725E76-239B-411F-9E09-B19577DC4C41}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{0FBCC40A-F2FC-48B1-AFDC-AF256BA67F47}" name="person_id"/>
     <tableColumn id="2" xr3:uid="{B8A1BF6E-529F-4B1B-83B9-36B3C0D9E941}" name="name"/>
     <tableColumn id="3" xr3:uid="{4EE53A3A-B714-47ED-B4BC-B9F59726A744}" name="addr"/>
-    <tableColumn id="4" xr3:uid="{0153F1B2-390B-4E9D-9217-7EDE86D2FDEE}" name="cus_date" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{51636820-D4A1-44D8-A773-FE4F3F4ABA6B}" name="phone"/>
+    <tableColumn id="4" xr3:uid="{0153F1B2-390B-4E9D-9217-7EDE86D2FDEE}" name="cus_date" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{51636820-D4A1-44D8-A773-FE4F3F4ABA6B}" name="phone" dataDxfId="0"/>
     <tableColumn id="6" xr3:uid="{A49D98AD-4193-4BEB-B898-697D3B181E7F}" name="role"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -754,7 +761,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
@@ -873,7 +880,7 @@
         <v>3</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -951,7 +958,7 @@
         <v>6</v>
       </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -1003,7 +1010,7 @@
         <v>7</v>
       </c>
       <c r="G10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -1029,7 +1036,7 @@
         <v>7</v>
       </c>
       <c r="G11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -1107,7 +1114,7 @@
         <v>9</v>
       </c>
       <c r="G14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -1133,7 +1140,7 @@
         <v>10</v>
       </c>
       <c r="G15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -1185,7 +1192,7 @@
         <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -1211,7 +1218,7 @@
         <v>12</v>
       </c>
       <c r="G18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -1237,7 +1244,7 @@
         <v>12</v>
       </c>
       <c r="G19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -1289,7 +1296,7 @@
         <v>13</v>
       </c>
       <c r="G21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -1315,7 +1322,7 @@
         <v>14</v>
       </c>
       <c r="G22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H22">
         <v>2</v>
@@ -1341,7 +1348,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -1367,7 +1374,7 @@
         <v>16</v>
       </c>
       <c r="G24" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -1393,7 +1400,7 @@
         <v>16</v>
       </c>
       <c r="G25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -1445,7 +1452,7 @@
         <v>17</v>
       </c>
       <c r="G27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -1471,7 +1478,7 @@
         <v>18</v>
       </c>
       <c r="G28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -1497,7 +1504,7 @@
         <v>19</v>
       </c>
       <c r="G29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -1523,7 +1530,7 @@
         <v>19</v>
       </c>
       <c r="G30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -1549,7 +1556,7 @@
         <v>20</v>
       </c>
       <c r="G31" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -1575,7 +1582,7 @@
         <v>20</v>
       </c>
       <c r="G32" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -1589,7 +1596,7 @@
         <v>46082</v>
       </c>
       <c r="C33" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D33">
         <v>12000</v>
@@ -1618,7 +1625,7 @@
         <v>11</v>
       </c>
       <c r="G34" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H34">
         <v>12</v>
@@ -1641,7 +1648,7 @@
         <v>11</v>
       </c>
       <c r="G35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H35">
         <v>5</v>
@@ -1710,7 +1717,7 @@
         <v>11</v>
       </c>
       <c r="G38" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H38">
         <v>5</v>
@@ -1733,7 +1740,7 @@
         <v>11</v>
       </c>
       <c r="G39" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H39">
         <v>9</v>
@@ -1756,7 +1763,7 @@
         <v>11</v>
       </c>
       <c r="G40" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H40">
         <v>4</v>
@@ -1779,10 +1786,50 @@
         <v>11</v>
       </c>
       <c r="G41" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H41">
         <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" s="1">
+        <v>46081</v>
+      </c>
+      <c r="C42" t="s">
+        <v>75</v>
+      </c>
+      <c r="D42">
+        <v>5000</v>
+      </c>
+      <c r="E42" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" s="1">
+        <v>46090</v>
+      </c>
+      <c r="C43" t="s">
+        <v>75</v>
+      </c>
+      <c r="D43">
+        <v>5000</v>
+      </c>
+      <c r="E43" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1802,7 +1849,7 @@
     <col min="2" max="2" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1811,19 +1858,19 @@
         <v>5</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -1831,13 +1878,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1845,19 +1892,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D3" s="1">
         <v>46081</v>
       </c>
-      <c r="E3" t="s">
-        <v>52</v>
+      <c r="E3" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="F3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1865,19 +1912,19 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D4" s="1">
         <v>46081</v>
       </c>
-      <c r="E4" t="s">
-        <v>53</v>
+      <c r="E4" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="F4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1885,19 +1932,19 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D5" s="1">
         <v>46081</v>
       </c>
-      <c r="E5" t="s">
-        <v>54</v>
+      <c r="E5" s="4" t="s">
+        <v>53</v>
       </c>
       <c r="F5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1905,19 +1952,19 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D6" s="1">
         <v>46081</v>
       </c>
-      <c r="E6" t="s">
-        <v>55</v>
+      <c r="E6" s="4" t="s">
+        <v>54</v>
       </c>
       <c r="F6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1925,19 +1972,19 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D7" s="1">
         <v>46081</v>
       </c>
-      <c r="E7" t="s">
-        <v>56</v>
+      <c r="E7" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="F7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1945,19 +1992,19 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D8" s="1">
         <v>46081</v>
       </c>
-      <c r="E8" t="s">
-        <v>57</v>
+      <c r="E8" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="F8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1965,19 +2012,19 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D9" s="1">
         <v>46081</v>
       </c>
-      <c r="E9" t="s">
-        <v>58</v>
+      <c r="E9" s="4" t="s">
+        <v>57</v>
       </c>
       <c r="F9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1985,19 +2032,19 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D10" s="1">
         <v>46081</v>
       </c>
-      <c r="E10" t="s">
-        <v>59</v>
+      <c r="E10" s="4" t="s">
+        <v>58</v>
       </c>
       <c r="F10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -2005,19 +2052,19 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D11" s="1">
         <v>46081</v>
       </c>
-      <c r="E11" t="s">
-        <v>60</v>
+      <c r="E11" s="4" t="s">
+        <v>59</v>
       </c>
       <c r="F11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -2025,19 +2072,19 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" s="1">
         <v>46081</v>
       </c>
-      <c r="E12" t="s">
-        <v>61</v>
+      <c r="E12" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="F12" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -2045,19 +2092,19 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D13" s="1">
         <v>46081</v>
       </c>
-      <c r="E13" t="s">
-        <v>62</v>
+      <c r="E13" s="4" t="s">
+        <v>61</v>
       </c>
       <c r="F13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -2065,19 +2112,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D14" s="1">
         <v>46081</v>
       </c>
-      <c r="E14" t="s">
-        <v>63</v>
+      <c r="E14" s="4" t="s">
+        <v>62</v>
       </c>
       <c r="F14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -2085,19 +2132,19 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" s="1">
         <v>46081</v>
       </c>
-      <c r="E15" t="s">
-        <v>64</v>
+      <c r="E15" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="F15" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -2105,19 +2152,19 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" s="1">
         <v>46081</v>
       </c>
-      <c r="E16" t="s">
-        <v>65</v>
+      <c r="E16" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="F16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -2125,19 +2172,19 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D17" s="1">
         <v>46081</v>
       </c>
-      <c r="E17" t="s">
-        <v>66</v>
+      <c r="E17" s="4" t="s">
+        <v>65</v>
       </c>
       <c r="F17" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -2145,19 +2192,19 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D18" s="1">
         <v>46081</v>
       </c>
-      <c r="E18" t="s">
-        <v>67</v>
+      <c r="E18" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="F18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -2165,19 +2212,19 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D19" s="1">
         <v>46083</v>
       </c>
-      <c r="E19" t="s">
-        <v>68</v>
+      <c r="E19" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="F19" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -2185,19 +2232,19 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D20" s="1">
         <v>46083</v>
       </c>
-      <c r="E20" t="s">
-        <v>69</v>
+      <c r="E20" s="4" t="s">
+        <v>74</v>
       </c>
       <c r="F20" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -2205,19 +2252,19 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D21" s="1">
         <v>46083</v>
       </c>
-      <c r="E21" t="s">
-        <v>70</v>
+      <c r="E21" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="F21" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -2225,19 +2272,19 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D22" s="1">
         <v>46083</v>
       </c>
-      <c r="E22" t="s">
-        <v>71</v>
+      <c r="E22" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="F22" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -2245,23 +2292,27 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D23" s="1">
         <v>46083</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F23" t="s">
         <v>72</v>
       </c>
-      <c r="F23" t="s">
-        <v>74</v>
-      </c>
     </row>
   </sheetData>
+  <dataConsolidate/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="E3:E19 E21:E24" numberStoredAsText="1"/>
+  </ignoredErrors>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>

--- a/data2.xlsx
+++ b/data2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\rejoice\data_projects\crucial_sales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A77EDDC-4A5E-49BF-8A67-220491EE6E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5386371-A92C-4182-ACEC-7A485ECF8B36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transactions" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="77">
   <si>
     <t>txn_id</t>
   </si>
@@ -260,6 +260,9 @@
   </si>
   <si>
     <t>salaries</t>
+  </si>
+  <si>
+    <t>capital</t>
   </si>
 </sst>
 </file>
@@ -443,8 +446,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5687A707-2FB8-42A8-86F4-54A8763C6A1B}" name="Table1" displayName="Table1" ref="A1:H43" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6">
-  <autoFilter ref="A1:H43" xr:uid="{5687A707-2FB8-42A8-86F4-54A8763C6A1B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5687A707-2FB8-42A8-86F4-54A8763C6A1B}" name="Table1" displayName="Table1" ref="A1:H44" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6">
+  <autoFilter ref="A1:H44" xr:uid="{5687A707-2FB8-42A8-86F4-54A8763C6A1B}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{C0FD0D9F-9597-4679-9F73-63FF804A0881}" name="txn_id"/>
     <tableColumn id="2" xr3:uid="{FF9D134A-CB66-4B80-9E10-D3C9D3780E4A}" name="date" dataDxfId="5"/>
@@ -761,7 +764,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
@@ -772,6 +775,8 @@
     <col min="6" max="6" width="13.77734375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -1817,7 +1822,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="1">
-        <v>46090</v>
+        <v>46084</v>
       </c>
       <c r="C43" t="s">
         <v>75</v>
@@ -1829,6 +1834,26 @@
         <v>11</v>
       </c>
       <c r="F43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" s="1">
+        <v>46078</v>
+      </c>
+      <c r="C44" t="s">
+        <v>76</v>
+      </c>
+      <c r="D44">
+        <v>78500</v>
+      </c>
+      <c r="E44" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44">
         <v>0</v>
       </c>
     </row>
